--- a/Output Files GPT-OSS 20B/position_bias/position_bias_summary_gptoss.xlsx
+++ b/Output Files GPT-OSS 20B/position_bias/position_bias_summary_gptoss.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,790 +1267,6 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.2704</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0419</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.2376</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.3436</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.2379</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3231</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0285</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.4564</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5179</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.1569</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-5.51</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.6308</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.7692</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.7333</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7949000000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.1384</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-5.89</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.0308</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2897</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.2615</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.3667</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.2589</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-5.89</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2647</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.0514</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.2647</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-5.15</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4686</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.4143</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5143</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-0.1829</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-4.95</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.6429</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.7743</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.7286</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.8143</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.1314</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.3014</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.0581</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.2143</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.3714</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.3014</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.2308</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.0482</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0752</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.1385</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0462</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-0.1826</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.3046</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.2615</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.3385</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-0.1046</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.4462</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.5939</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.0592</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.4923</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.6462</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-0.1477</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>-0.2538</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.0769</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.07829999999999999</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.1692</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.0231</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.1769</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-2.26</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.3556</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6222</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0333</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.5889</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.6778</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-0.2666</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-8</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.6834</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.6167</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.7667</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-0.1834</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>top2_accuracy</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.8167</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.9533</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.9333</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-0.1366</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.6733</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.6333</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.7333</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-0.2983</v>
-      </c>
-      <c r="J33" t="n">
-        <v>-8.07</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>5</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
